--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,12 +131,6 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -214,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -283,9 +277,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5435,23 +5426,19 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>43411</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5460,12 +5447,12 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
@@ -5475,7 +5462,7 @@
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9122,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9145,7 +9132,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9525,12 +9512,12 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 645呎 (2房)
-招标单位
--
-(在售)</t>
+$2800万
+$43,411/呎
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -9517,7 +9517,7 @@
           <t>B | 645呎 (2房)
 $2800万
 $43,411/呎
-(26年-09月-07日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,6 +131,12 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -208,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -277,6 +283,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1845,7 +1854,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1911,7 +1920,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1972,7 +1981,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1982,12 +1991,12 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1997,12 +2006,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2012,7 +2021,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3419,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -3420,12 +3429,12 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -3435,12 +3444,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -3450,7 +3459,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8608,14 +8617,14 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
           <t>21</t>
@@ -8623,7 +8632,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -8853,7 +8862,7 @@
           <t>A | 1679呎 (4+房)
 $8480万
 $50,506/呎
-(26年-08月-31日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -8861,7 +8870,7 @@
           <t>B | 1686呎 (4+房)
 $8400万
 $49,822/呎
-(26年-08月-31日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
     </row>
@@ -8879,12 +8888,12 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>B | 1686呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -9122,14 +9131,14 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
           <t>25</t>
@@ -9142,7 +9151,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -9230,12 +9239,12 @@
 (25年-09月-16日)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>B | 645呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,12 +131,6 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -214,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -283,9 +277,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1981,23 +1972,19 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>84680000</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>50225</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
@@ -2006,12 +1993,12 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2021,7 +2008,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3419,23 +3406,19 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>30380000</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>47101</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3444,12 +3427,12 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
@@ -3459,7 +3442,7 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8617,7 +8600,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -8627,7 +8610,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -8888,12 +8871,12 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 1686呎 (4+房)
-招标单位
--
-(在售)</t>
+$8468万
+$50,225/呎
+(26年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -9131,7 +9114,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9141,7 +9124,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9239,12 +9222,12 @@
 (25年-09月-16日)</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 645呎 (2房)
-招标单位
--
-(在售)</t>
+$3038万
+$47,101/呎
+(26年-09月-28日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,6 +131,12 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -208,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -277,6 +283,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3868,7 +3877,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3878,12 +3887,12 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -3893,12 +3902,12 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -3908,7 +3917,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9114,14 +9123,14 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
           <t>26</t>
@@ -9134,7 +9143,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -9340,12 +9349,12 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>E | 439呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -2113,7 +2113,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2123,12 +2123,12 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="H49" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -3902,12 +3902,12 @@
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8609,14 +8609,14 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
           <t>22</t>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -8903,12 +8903,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>B | 1686呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -8926,12 +8926,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>B | 1686呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -9349,12 +9349,12 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 439呎 (2房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
+++ b/files/港岛-渣甸山及黄泥涌峡-峻誉．渣甸山.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,12 +131,6 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -214,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -283,9 +277,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1986,7 +1977,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2113,7 +2104,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2123,12 +2114,12 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2138,12 +2129,12 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2153,7 +2144,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2244,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2263,12 +2254,12 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2278,12 +2269,12 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -2293,7 +2284,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3877,23 +3868,19 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>24880000</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>56674</v>
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
@@ -8609,27 +8596,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8872,7 @@
           <t>B | 1686呎 (4+房)
 $8468万
 $50,225/呎
-(26年-09月-28日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
     </row>
@@ -8903,12 +8890,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 1686呎 (4+房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -8926,12 +8913,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 1686呎 (4+房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9120,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9143,7 +9130,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -9349,12 +9336,12 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 439呎 (2房)
--
--
-(待售)</t>
+$2488万
+$56,674/呎
+(26年-10月-09日)</t>
         </is>
       </c>
     </row>
